--- a/results/components/gene_names/p6s3.xlsx
+++ b/results/components/gene_names/p6s3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="164">
   <si>
     <t>gene1</t>
   </si>
@@ -22,484 +22,490 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Psn</t>
-  </si>
-  <si>
-    <t>Ark</t>
-  </si>
-  <si>
-    <t>sle</t>
-  </si>
-  <si>
-    <t>tral</t>
-  </si>
-  <si>
-    <t>Aph-4</t>
-  </si>
-  <si>
-    <t>poe</t>
+    <t>Ef1gamma</t>
+  </si>
+  <si>
+    <t>tin</t>
+  </si>
+  <si>
+    <t>MED11</t>
+  </si>
+  <si>
+    <t>Cks30A</t>
+  </si>
+  <si>
+    <t>Rack1</t>
+  </si>
+  <si>
+    <t>Hem</t>
+  </si>
+  <si>
+    <t>sty</t>
+  </si>
+  <si>
+    <t>CG9520</t>
+  </si>
+  <si>
+    <t>Antp</t>
+  </si>
+  <si>
+    <t>Dhc64C</t>
+  </si>
+  <si>
+    <t>Moe</t>
+  </si>
+  <si>
+    <t>Cyt-c-d</t>
+  </si>
+  <si>
+    <t>Set2</t>
+  </si>
+  <si>
+    <t>Pvr</t>
+  </si>
+  <si>
+    <t>l(2)efl</t>
+  </si>
+  <si>
+    <t>tld</t>
+  </si>
+  <si>
+    <t>apt</t>
+  </si>
+  <si>
+    <t>Chc</t>
+  </si>
+  <si>
+    <t>Abd-B</t>
+  </si>
+  <si>
+    <t>fs(2)ltoPP43</t>
+  </si>
+  <si>
+    <t>dsf</t>
   </si>
   <si>
     <t>Su(var)2-10</t>
   </si>
   <si>
-    <t>mbl</t>
+    <t>Pk92B</t>
+  </si>
+  <si>
+    <t>dpp</t>
+  </si>
+  <si>
+    <t>l(3)mbt</t>
+  </si>
+  <si>
+    <t>Dok</t>
+  </si>
+  <si>
+    <t>tub</t>
+  </si>
+  <si>
+    <t>CG2681</t>
+  </si>
+  <si>
+    <t>Sur</t>
+  </si>
+  <si>
+    <t>beta4GalNAcTA</t>
+  </si>
+  <si>
+    <t>Sobp</t>
+  </si>
+  <si>
+    <t>Atpalpha</t>
+  </si>
+  <si>
+    <t>ecd</t>
+  </si>
+  <si>
+    <t>dei</t>
+  </si>
+  <si>
+    <t>eg</t>
+  </si>
+  <si>
+    <t>Dif</t>
+  </si>
+  <si>
+    <t>Rca1</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>Sema-2a</t>
+  </si>
+  <si>
+    <t>cbt</t>
+  </si>
+  <si>
+    <t>CG12301</t>
+  </si>
+  <si>
+    <t>Idgf4</t>
+  </si>
+  <si>
+    <t>ine</t>
+  </si>
+  <si>
+    <t>Cka</t>
+  </si>
+  <si>
+    <t>up</t>
+  </si>
+  <si>
+    <t>asf1</t>
+  </si>
+  <si>
+    <t>Galpha73B</t>
+  </si>
+  <si>
+    <t>cathD</t>
+  </si>
+  <si>
+    <t>phyl</t>
+  </si>
+  <si>
+    <t>bnl</t>
+  </si>
+  <si>
+    <t>betaTub56D</t>
+  </si>
+  <si>
+    <t>chif</t>
+  </si>
+  <si>
+    <t>cin</t>
+  </si>
+  <si>
+    <t>Tak1</t>
+  </si>
+  <si>
+    <t>Mmp1</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>cta</t>
+  </si>
+  <si>
+    <t>bt</t>
+  </si>
+  <si>
+    <t>esg</t>
+  </si>
+  <si>
+    <t>pav</t>
+  </si>
+  <si>
+    <t>pn</t>
+  </si>
+  <si>
+    <t>Yp1</t>
+  </si>
+  <si>
+    <t>tow</t>
+  </si>
+  <si>
+    <t>Apc</t>
+  </si>
+  <si>
+    <t>Myo61F</t>
+  </si>
+  <si>
+    <t>jar</t>
+  </si>
+  <si>
+    <t>lic</t>
+  </si>
+  <si>
+    <t>l(1)G0289</t>
+  </si>
+  <si>
+    <t>Myo31DF</t>
+  </si>
+  <si>
+    <t>Iswi</t>
+  </si>
+  <si>
+    <t>eIF-4E</t>
+  </si>
+  <si>
+    <t>knrl</t>
+  </si>
+  <si>
+    <t>nmo</t>
+  </si>
+  <si>
+    <t>PebIII</t>
+  </si>
+  <si>
+    <t>sgg</t>
+  </si>
+  <si>
+    <t>pot</t>
+  </si>
+  <si>
+    <t>Nrt</t>
+  </si>
+  <si>
+    <t>aft</t>
+  </si>
+  <si>
+    <t>ImpE3</t>
+  </si>
+  <si>
+    <t>zfh1</t>
+  </si>
+  <si>
+    <t>zfh2</t>
+  </si>
+  <si>
+    <t>boss</t>
+  </si>
+  <si>
+    <t>kis</t>
   </si>
   <si>
     <t>Lcp65Ag1</t>
   </si>
   <si>
-    <t>Myo31DF</t>
-  </si>
-  <si>
-    <t>vlc</t>
+    <t>tum</t>
+  </si>
+  <si>
+    <t>da</t>
+  </si>
+  <si>
+    <t>glu</t>
+  </si>
+  <si>
+    <t>Tina-1</t>
+  </si>
+  <si>
+    <t>MED24</t>
+  </si>
+  <si>
+    <t>Bap60</t>
+  </si>
+  <si>
+    <t>Dat</t>
   </si>
   <si>
     <t>bon</t>
   </si>
   <si>
-    <t>bnl</t>
-  </si>
-  <si>
-    <t>Ice</t>
+    <t>esc</t>
+  </si>
+  <si>
+    <t>SelD</t>
+  </si>
+  <si>
+    <t>CkIIalpha</t>
+  </si>
+  <si>
+    <t>lmd</t>
+  </si>
+  <si>
+    <t>dah</t>
+  </si>
+  <si>
+    <t>l(2)gd1</t>
+  </si>
+  <si>
+    <t>flw</t>
+  </si>
+  <si>
+    <t>fw</t>
+  </si>
+  <si>
+    <t>CadN</t>
+  </si>
+  <si>
+    <t>form3</t>
+  </si>
+  <si>
+    <t>ash1</t>
+  </si>
+  <si>
+    <t>fog</t>
+  </si>
+  <si>
+    <t>Syx1A</t>
+  </si>
+  <si>
+    <t>rad50</t>
+  </si>
+  <si>
+    <t>sec23</t>
+  </si>
+  <si>
+    <t>sas</t>
+  </si>
+  <si>
+    <t>spen</t>
+  </si>
+  <si>
+    <t>gl</t>
+  </si>
+  <si>
+    <t>hpo</t>
+  </si>
+  <si>
+    <t>Eip63E</t>
+  </si>
+  <si>
+    <t>abd-A</t>
+  </si>
+  <si>
+    <t>dnc</t>
+  </si>
+  <si>
+    <t>eff</t>
+  </si>
+  <si>
+    <t>SelG</t>
+  </si>
+  <si>
+    <t>cnc</t>
+  </si>
+  <si>
+    <t>numb</t>
+  </si>
+  <si>
+    <t>how</t>
+  </si>
+  <si>
+    <t>Dad</t>
+  </si>
+  <si>
+    <t>foxo</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>Lac</t>
+  </si>
+  <si>
+    <t>Sry-delta</t>
+  </si>
+  <si>
+    <t>Tm1</t>
+  </si>
+  <si>
+    <t>chic</t>
+  </si>
+  <si>
+    <t>Sb</t>
+  </si>
+  <si>
+    <t>siz</t>
+  </si>
+  <si>
+    <t>disco</t>
+  </si>
+  <si>
+    <t>frc</t>
+  </si>
+  <si>
+    <t>th</t>
+  </si>
+  <si>
+    <t>oaf</t>
+  </si>
+  <si>
+    <t>pnr</t>
+  </si>
+  <si>
+    <t>ofs</t>
+  </si>
+  <si>
+    <t>RpL30</t>
+  </si>
+  <si>
+    <t>E(z)</t>
+  </si>
+  <si>
+    <t>Dl</t>
+  </si>
+  <si>
+    <t>trc</t>
+  </si>
+  <si>
+    <t>Pgant35A</t>
   </si>
   <si>
     <t>rdo</t>
   </si>
   <si>
-    <t>cort</t>
-  </si>
-  <si>
-    <t>Sb</t>
+    <t>18w</t>
+  </si>
+  <si>
+    <t>Vhl</t>
+  </si>
+  <si>
+    <t>fal</t>
+  </si>
+  <si>
+    <t>elav</t>
+  </si>
+  <si>
+    <t>Pka-C3</t>
+  </si>
+  <si>
+    <t>ALiX</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>scra</t>
+  </si>
+  <si>
+    <t>sn</t>
+  </si>
+  <si>
+    <t>xmas-2</t>
+  </si>
+  <si>
+    <t>grp</t>
+  </si>
+  <si>
+    <t>dos</t>
+  </si>
+  <si>
+    <t>Dcp-1</t>
+  </si>
+  <si>
+    <t>cactin</t>
+  </si>
+  <si>
+    <t>hep</t>
+  </si>
+  <si>
+    <t>inaC</t>
+  </si>
+  <si>
+    <t>Oseg1</t>
+  </si>
+  <si>
+    <t>yrt</t>
+  </si>
+  <si>
+    <t>Hs6st</t>
   </si>
   <si>
     <t>Abl</t>
   </si>
   <si>
-    <t>oaf</t>
-  </si>
-  <si>
-    <t>morgue</t>
-  </si>
-  <si>
-    <t>yrt</t>
-  </si>
-  <si>
-    <t>dock</t>
-  </si>
-  <si>
-    <t>PebIII</t>
-  </si>
-  <si>
-    <t>Pvr</t>
-  </si>
-  <si>
-    <t>bib</t>
-  </si>
-  <si>
-    <t>rux</t>
-  </si>
-  <si>
-    <t>aft</t>
-  </si>
-  <si>
-    <t>cher</t>
-  </si>
-  <si>
-    <t>Rbp9</t>
-  </si>
-  <si>
-    <t>CG34417</t>
-  </si>
-  <si>
-    <t>by</t>
-  </si>
-  <si>
-    <t>MYPT-75D</t>
-  </si>
-  <si>
-    <t>Ank2</t>
-  </si>
-  <si>
-    <t>mus304</t>
-  </si>
-  <si>
-    <t>shrb</t>
-  </si>
-  <si>
-    <t>CSN4</t>
-  </si>
-  <si>
-    <t>how</t>
-  </si>
-  <si>
-    <t>sktl</t>
-  </si>
-  <si>
-    <t>jumu</t>
-  </si>
-  <si>
-    <t>Akt1</t>
-  </si>
-  <si>
-    <t>Rack1</t>
-  </si>
-  <si>
-    <t>Dcp-1</t>
-  </si>
-  <si>
-    <t>ix</t>
-  </si>
-  <si>
-    <t>Dhc64C</t>
-  </si>
-  <si>
-    <t>noc</t>
-  </si>
-  <si>
-    <t>dah</t>
-  </si>
-  <si>
-    <t>sqd</t>
-  </si>
-  <si>
-    <t>Patj</t>
-  </si>
-  <si>
-    <t>fred</t>
-  </si>
-  <si>
-    <t>ine</t>
-  </si>
-  <si>
-    <t>dmt</t>
-  </si>
-  <si>
-    <t>bnb</t>
-  </si>
-  <si>
-    <t>fru</t>
-  </si>
-  <si>
-    <t>spin</t>
-  </si>
-  <si>
-    <t>dj</t>
-  </si>
-  <si>
-    <t>par-6</t>
-  </si>
-  <si>
-    <t>nej</t>
-  </si>
-  <si>
-    <t>rib</t>
-  </si>
-  <si>
-    <t>trn</t>
-  </si>
-  <si>
-    <t>Dat</t>
-  </si>
-  <si>
-    <t>dl</t>
-  </si>
-  <si>
-    <t>Mmp1</t>
-  </si>
-  <si>
-    <t>cathD</t>
-  </si>
-  <si>
-    <t>CG12301</t>
-  </si>
-  <si>
-    <t>Khc</t>
-  </si>
-  <si>
-    <t>bowl</t>
-  </si>
-  <si>
-    <t>Gtp-bp</t>
-  </si>
-  <si>
-    <t>Caf1</t>
-  </si>
-  <si>
-    <t>Sema-2a</t>
-  </si>
-  <si>
-    <t>ninaE</t>
-  </si>
-  <si>
-    <t>stg</t>
-  </si>
-  <si>
-    <t>Axn</t>
-  </si>
-  <si>
-    <t>spir</t>
-  </si>
-  <si>
-    <t>mfas</t>
-  </si>
-  <si>
-    <t>ena</t>
-  </si>
-  <si>
-    <t>E2f</t>
-  </si>
-  <si>
-    <t>sina</t>
-  </si>
-  <si>
-    <t>CtBP</t>
-  </si>
-  <si>
-    <t>car</t>
-  </si>
-  <si>
-    <t>Pcaf</t>
-  </si>
-  <si>
-    <t>loco</t>
-  </si>
-  <si>
-    <t>18w</t>
-  </si>
-  <si>
-    <t>Cks30A</t>
-  </si>
-  <si>
-    <t>Lis-1</t>
-  </si>
-  <si>
-    <t>sns</t>
-  </si>
-  <si>
-    <t>frc</t>
-  </si>
-  <si>
-    <t>peb</t>
-  </si>
-  <si>
-    <t>stil</t>
-  </si>
-  <si>
-    <t>Ald</t>
-  </si>
-  <si>
-    <t>ash1</t>
-  </si>
-  <si>
-    <t>Not1</t>
-  </si>
-  <si>
-    <t>CG9445</t>
-  </si>
-  <si>
-    <t>glu</t>
-  </si>
-  <si>
-    <t>betaTub56D</t>
-  </si>
-  <si>
-    <t>mask</t>
-  </si>
-  <si>
-    <t>ksr</t>
-  </si>
-  <si>
-    <t>puc</t>
-  </si>
-  <si>
-    <t>cnc</t>
-  </si>
-  <si>
-    <t>Tak1</t>
-  </si>
-  <si>
-    <t>Mitf</t>
-  </si>
-  <si>
-    <t>cin</t>
-  </si>
-  <si>
-    <t>thr</t>
-  </si>
-  <si>
-    <t>ttk</t>
-  </si>
-  <si>
-    <t>ALiX</t>
-  </si>
-  <si>
-    <t>CG6416</t>
-  </si>
-  <si>
-    <t>CG9509</t>
-  </si>
-  <si>
-    <t>Idgf2</t>
-  </si>
-  <si>
-    <t>drm</t>
-  </si>
-  <si>
-    <t>Oseg1</t>
-  </si>
-  <si>
-    <t>Syx1A</t>
-  </si>
-  <si>
-    <t>pyd</t>
-  </si>
-  <si>
-    <t>wal</t>
-  </si>
-  <si>
-    <t>Pak</t>
-  </si>
-  <si>
-    <t>dnc</t>
-  </si>
-  <si>
-    <t>fal</t>
-  </si>
-  <si>
-    <t>twi</t>
-  </si>
-  <si>
-    <t>cbt</t>
-  </si>
-  <si>
-    <t>eff</t>
+    <t>Sh</t>
   </si>
   <si>
     <t>Fas3</t>
-  </si>
-  <si>
-    <t>odd</t>
-  </si>
-  <si>
-    <t>emb</t>
-  </si>
-  <si>
-    <t>Prm</t>
-  </si>
-  <si>
-    <t>Mer</t>
-  </si>
-  <si>
-    <t>Mlc1</t>
-  </si>
-  <si>
-    <t>CG3987</t>
-  </si>
-  <si>
-    <t>E2f2</t>
-  </si>
-  <si>
-    <t>her</t>
-  </si>
-  <si>
-    <t>th</t>
-  </si>
-  <si>
-    <t>abd-A</t>
-  </si>
-  <si>
-    <t>qua</t>
-  </si>
-  <si>
-    <t>ftz-f1</t>
-  </si>
-  <si>
-    <t>wls</t>
-  </si>
-  <si>
-    <t>dome</t>
-  </si>
-  <si>
-    <t>RpL30</t>
-  </si>
-  <si>
-    <t>FKBP59</t>
-  </si>
-  <si>
-    <t>cas</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>pot</t>
-  </si>
-  <si>
-    <t>CadN</t>
-  </si>
-  <si>
-    <t>Mmp2</t>
-  </si>
-  <si>
-    <t>dom</t>
-  </si>
-  <si>
-    <t>fd59A</t>
-  </si>
-  <si>
-    <t>MED4</t>
-  </si>
-  <si>
-    <t>Ggamma1</t>
-  </si>
-  <si>
-    <t>CG13850</t>
-  </si>
-  <si>
-    <t>pnr</t>
-  </si>
-  <si>
-    <t>Pk92B</t>
-  </si>
-  <si>
-    <t>ics</t>
-  </si>
-  <si>
-    <t>brat</t>
-  </si>
-  <si>
-    <t>rhea</t>
-  </si>
-  <si>
-    <t>Myo61F</t>
-  </si>
-  <si>
-    <t>Eip74EF</t>
-  </si>
-  <si>
-    <t>p53</t>
-  </si>
-  <si>
-    <t>hpo</t>
-  </si>
-  <si>
-    <t>CG3075</t>
-  </si>
-  <si>
-    <t>tok</t>
-  </si>
-  <si>
-    <t>fw</t>
-  </si>
-  <si>
-    <t>Crk</t>
-  </si>
-  <si>
-    <t>CG17739</t>
-  </si>
-  <si>
-    <t>kkv</t>
   </si>
 </sst>
 </file>
@@ -831,7 +837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B99"/>
+  <dimension ref="A1:B104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -927,420 +933,420 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" t="s">
         <v>57</v>
-      </c>
-      <c r="B32" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B36" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="B40" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B42" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B43" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B44" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="B45" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B48" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B49" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B50" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B52" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B53" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B55" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B56" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B57" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B58" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B59" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="B60" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B61" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B62" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B63" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B64" t="s">
         <v>111</v>
@@ -1348,23 +1354,23 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
+        <v>93</v>
+      </c>
+      <c r="B65" t="s">
         <v>112</v>
-      </c>
-      <c r="B65" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B66" t="s">
         <v>114</v>
-      </c>
-      <c r="B66" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c r="B67" t="s">
         <v>116</v>
@@ -1372,23 +1378,23 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="B68" t="s">
-        <v>39</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B69" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>119</v>
+        <v>43</v>
       </c>
       <c r="B70" t="s">
         <v>120</v>
@@ -1396,10 +1402,10 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
+        <v>17</v>
+      </c>
+      <c r="B71" t="s">
         <v>121</v>
-      </c>
-      <c r="B71" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1407,12 +1413,12 @@
         <v>122</v>
       </c>
       <c r="B72" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="B73" t="s">
         <v>124</v>
@@ -1420,210 +1426,250 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="B74" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="B75" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>129</v>
+        <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B77" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B78" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="B79" t="s">
-        <v>135</v>
+        <v>18</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B80" t="s">
-        <v>137</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="B81" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>52</v>
+        <v>135</v>
       </c>
       <c r="B82" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B83" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="B84" t="s">
-        <v>8</v>
+        <v>139</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="B85" t="s">
-        <v>3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="B86" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="B87" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>145</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>146</v>
+        <v>72</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>54</v>
+        <v>143</v>
       </c>
       <c r="B89" t="s">
-        <v>53</v>
+        <v>144</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="B90" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>148</v>
+        <v>72</v>
       </c>
       <c r="B91" t="s">
-        <v>149</v>
+        <v>110</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B92" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B93" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B94" t="s">
-        <v>154</v>
+        <v>28</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="B95" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="B96" t="s">
-        <v>156</v>
+        <v>90</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="B97" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B98" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
+        <v>155</v>
+      </c>
+      <c r="B99" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>156</v>
+      </c>
+      <c r="B100" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>106</v>
+      </c>
+      <c r="B101" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" t="s">
+        <v>159</v>
+      </c>
+      <c r="B102" t="s">
         <v>160</v>
       </c>
-      <c r="B99" t="s">
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
         <v>161</v>
+      </c>
+      <c r="B103" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>163</v>
+      </c>
+      <c r="B104" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/results/components/gene_names/p6s3.xlsx
+++ b/results/components/gene_names/p6s3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="112">
   <si>
     <t>gene1</t>
   </si>
@@ -22,490 +22,334 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Ef1gamma</t>
-  </si>
-  <si>
-    <t>tin</t>
-  </si>
-  <si>
-    <t>MED11</t>
-  </si>
-  <si>
-    <t>Cks30A</t>
-  </si>
-  <si>
-    <t>Rack1</t>
-  </si>
-  <si>
-    <t>Hem</t>
-  </si>
-  <si>
-    <t>sty</t>
-  </si>
-  <si>
-    <t>CG9520</t>
-  </si>
-  <si>
-    <t>Antp</t>
-  </si>
-  <si>
-    <t>Dhc64C</t>
+    <t>E(bx)</t>
+  </si>
+  <si>
+    <t>Su(z)12</t>
+  </si>
+  <si>
+    <t>Idgf5</t>
+  </si>
+  <si>
+    <t>trio</t>
+  </si>
+  <si>
+    <t>kuk</t>
+  </si>
+  <si>
+    <t>neur</t>
+  </si>
+  <si>
+    <t>Rpd3</t>
+  </si>
+  <si>
+    <t>dpld</t>
+  </si>
+  <si>
+    <t>dom</t>
+  </si>
+  <si>
+    <t>l(3)mbt</t>
+  </si>
+  <si>
+    <t>tld</t>
+  </si>
+  <si>
+    <t>CG10641</t>
+  </si>
+  <si>
+    <t>Rab5</t>
+  </si>
+  <si>
+    <t>mmy</t>
+  </si>
+  <si>
+    <t>tou</t>
+  </si>
+  <si>
+    <t>Mmp2</t>
+  </si>
+  <si>
+    <t>bap</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Khc</t>
+  </si>
+  <si>
+    <t>bowl</t>
   </si>
   <si>
     <t>Moe</t>
   </si>
   <si>
-    <t>Cyt-c-d</t>
+    <t>fd59A</t>
+  </si>
+  <si>
+    <t>puc</t>
+  </si>
+  <si>
+    <t>tra2</t>
+  </si>
+  <si>
+    <t>by</t>
+  </si>
+  <si>
+    <t>sgg</t>
+  </si>
+  <si>
+    <t>Rab7</t>
+  </si>
+  <si>
+    <t>cathD</t>
+  </si>
+  <si>
+    <t>tum</t>
+  </si>
+  <si>
+    <t>pbl</t>
+  </si>
+  <si>
+    <t>wee</t>
+  </si>
+  <si>
+    <t>wls</t>
+  </si>
+  <si>
+    <t>CG33205</t>
+  </si>
+  <si>
+    <t>CG16719</t>
+  </si>
+  <si>
+    <t>da</t>
+  </si>
+  <si>
+    <t>glu</t>
+  </si>
+  <si>
+    <t>CycE</t>
+  </si>
+  <si>
+    <t>esc</t>
+  </si>
+  <si>
+    <t>alien</t>
+  </si>
+  <si>
+    <t>Dl</t>
+  </si>
+  <si>
+    <t>Stat92E</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>emp</t>
+  </si>
+  <si>
+    <t>cactin</t>
+  </si>
+  <si>
+    <t>Su(H)</t>
+  </si>
+  <si>
+    <t>spn-A</t>
+  </si>
+  <si>
+    <t>hpo</t>
+  </si>
+  <si>
+    <t>E(z)</t>
+  </si>
+  <si>
+    <t>Caf1</t>
+  </si>
+  <si>
+    <t>snf</t>
+  </si>
+  <si>
+    <t>Sema-2a</t>
+  </si>
+  <si>
+    <t>wal</t>
+  </si>
+  <si>
+    <t>Eip74EF</t>
+  </si>
+  <si>
+    <t>capu</t>
+  </si>
+  <si>
+    <t>RhoGAPp190</t>
+  </si>
+  <si>
+    <t>Abl</t>
+  </si>
+  <si>
+    <t>BicD</t>
+  </si>
+  <si>
+    <t>rux</t>
+  </si>
+  <si>
+    <t>bigmax</t>
+  </si>
+  <si>
+    <t>spin</t>
+  </si>
+  <si>
+    <t>Su(var)2-10</t>
+  </si>
+  <si>
+    <t>MYPT-75D</t>
+  </si>
+  <si>
+    <t>Pcaf</t>
+  </si>
+  <si>
+    <t>sls</t>
+  </si>
+  <si>
+    <t>Apc</t>
+  </si>
+  <si>
+    <t>Dad</t>
+  </si>
+  <si>
+    <t>mus304</t>
+  </si>
+  <si>
+    <t>tok</t>
+  </si>
+  <si>
+    <t>dmt</t>
+  </si>
+  <si>
+    <t>asf1</t>
+  </si>
+  <si>
+    <t>lva</t>
+  </si>
+  <si>
+    <t>ttk</t>
+  </si>
+  <si>
+    <t>crol</t>
+  </si>
+  <si>
+    <t>tral</t>
+  </si>
+  <si>
+    <t>tamo</t>
+  </si>
+  <si>
+    <t>fw</t>
+  </si>
+  <si>
+    <t>amx</t>
+  </si>
+  <si>
+    <t>flfl</t>
+  </si>
+  <si>
+    <t>drm</t>
+  </si>
+  <si>
+    <t>CG1244</t>
+  </si>
+  <si>
+    <t>dl</t>
+  </si>
+  <si>
+    <t>numb</t>
+  </si>
+  <si>
+    <t>Rca1</t>
+  </si>
+  <si>
+    <t>hyx</t>
+  </si>
+  <si>
+    <t>RhoL</t>
+  </si>
+  <si>
+    <t>Pvr</t>
+  </si>
+  <si>
+    <t>raw</t>
   </si>
   <si>
     <t>Set2</t>
   </si>
   <si>
-    <t>Pvr</t>
-  </si>
-  <si>
-    <t>l(2)efl</t>
-  </si>
-  <si>
-    <t>tld</t>
-  </si>
-  <si>
-    <t>apt</t>
-  </si>
-  <si>
-    <t>Chc</t>
-  </si>
-  <si>
-    <t>Abd-B</t>
-  </si>
-  <si>
-    <t>fs(2)ltoPP43</t>
-  </si>
-  <si>
-    <t>dsf</t>
-  </si>
-  <si>
-    <t>Su(var)2-10</t>
-  </si>
-  <si>
-    <t>Pk92B</t>
-  </si>
-  <si>
-    <t>dpp</t>
-  </si>
-  <si>
-    <t>l(3)mbt</t>
-  </si>
-  <si>
-    <t>Dok</t>
-  </si>
-  <si>
-    <t>tub</t>
-  </si>
-  <si>
-    <t>CG2681</t>
-  </si>
-  <si>
-    <t>Sur</t>
-  </si>
-  <si>
-    <t>beta4GalNAcTA</t>
-  </si>
-  <si>
-    <t>Sobp</t>
-  </si>
-  <si>
-    <t>Atpalpha</t>
-  </si>
-  <si>
-    <t>ecd</t>
-  </si>
-  <si>
-    <t>dei</t>
-  </si>
-  <si>
-    <t>eg</t>
-  </si>
-  <si>
-    <t>Dif</t>
-  </si>
-  <si>
-    <t>Rca1</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>Sema-2a</t>
-  </si>
-  <si>
-    <t>cbt</t>
-  </si>
-  <si>
-    <t>CG12301</t>
-  </si>
-  <si>
-    <t>Idgf4</t>
-  </si>
-  <si>
-    <t>ine</t>
-  </si>
-  <si>
-    <t>Cka</t>
-  </si>
-  <si>
-    <t>up</t>
-  </si>
-  <si>
-    <t>asf1</t>
-  </si>
-  <si>
-    <t>Galpha73B</t>
-  </si>
-  <si>
-    <t>cathD</t>
-  </si>
-  <si>
-    <t>phyl</t>
-  </si>
-  <si>
-    <t>bnl</t>
-  </si>
-  <si>
-    <t>betaTub56D</t>
-  </si>
-  <si>
-    <t>chif</t>
-  </si>
-  <si>
-    <t>cin</t>
-  </si>
-  <si>
-    <t>Tak1</t>
-  </si>
-  <si>
-    <t>Mmp1</t>
-  </si>
-  <si>
-    <t>v</t>
-  </si>
-  <si>
-    <t>cta</t>
-  </si>
-  <si>
-    <t>bt</t>
-  </si>
-  <si>
-    <t>esg</t>
-  </si>
-  <si>
-    <t>pav</t>
-  </si>
-  <si>
-    <t>pn</t>
-  </si>
-  <si>
-    <t>Yp1</t>
+    <t>Wnt5</t>
+  </si>
+  <si>
+    <t>chp</t>
+  </si>
+  <si>
+    <t>Tm1</t>
+  </si>
+  <si>
+    <t>hep</t>
+  </si>
+  <si>
+    <t>ftz-f1</t>
+  </si>
+  <si>
+    <t>Pka-C3</t>
+  </si>
+  <si>
+    <t>gbb</t>
+  </si>
+  <si>
+    <t>Jafrac2</t>
+  </si>
+  <si>
+    <t>ninaE</t>
+  </si>
+  <si>
+    <t>Sxl</t>
+  </si>
+  <si>
+    <t>gl</t>
   </si>
   <si>
     <t>tow</t>
   </si>
   <si>
-    <t>Apc</t>
-  </si>
-  <si>
-    <t>Myo61F</t>
-  </si>
-  <si>
-    <t>jar</t>
-  </si>
-  <si>
-    <t>lic</t>
-  </si>
-  <si>
-    <t>l(1)G0289</t>
-  </si>
-  <si>
-    <t>Myo31DF</t>
-  </si>
-  <si>
-    <t>Iswi</t>
-  </si>
-  <si>
-    <t>eIF-4E</t>
-  </si>
-  <si>
-    <t>knrl</t>
-  </si>
-  <si>
-    <t>nmo</t>
-  </si>
-  <si>
-    <t>PebIII</t>
-  </si>
-  <si>
-    <t>sgg</t>
-  </si>
-  <si>
-    <t>pot</t>
-  </si>
-  <si>
-    <t>Nrt</t>
-  </si>
-  <si>
-    <t>aft</t>
-  </si>
-  <si>
-    <t>ImpE3</t>
-  </si>
-  <si>
-    <t>zfh1</t>
-  </si>
-  <si>
-    <t>zfh2</t>
-  </si>
-  <si>
-    <t>boss</t>
-  </si>
-  <si>
-    <t>kis</t>
-  </si>
-  <si>
-    <t>Lcp65Ag1</t>
-  </si>
-  <si>
-    <t>tum</t>
-  </si>
-  <si>
-    <t>da</t>
-  </si>
-  <si>
-    <t>glu</t>
-  </si>
-  <si>
-    <t>Tina-1</t>
-  </si>
-  <si>
-    <t>MED24</t>
-  </si>
-  <si>
-    <t>Bap60</t>
-  </si>
-  <si>
-    <t>Dat</t>
-  </si>
-  <si>
-    <t>bon</t>
-  </si>
-  <si>
-    <t>esc</t>
-  </si>
-  <si>
-    <t>SelD</t>
-  </si>
-  <si>
-    <t>CkIIalpha</t>
-  </si>
-  <si>
-    <t>lmd</t>
-  </si>
-  <si>
-    <t>dah</t>
-  </si>
-  <si>
-    <t>l(2)gd1</t>
-  </si>
-  <si>
-    <t>flw</t>
-  </si>
-  <si>
-    <t>fw</t>
-  </si>
-  <si>
-    <t>CadN</t>
+    <t>uzip</t>
+  </si>
+  <si>
+    <t>brm</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
   <si>
     <t>form3</t>
   </si>
   <si>
-    <t>ash1</t>
-  </si>
-  <si>
-    <t>fog</t>
-  </si>
-  <si>
-    <t>Syx1A</t>
-  </si>
-  <si>
-    <t>rad50</t>
-  </si>
-  <si>
-    <t>sec23</t>
-  </si>
-  <si>
-    <t>sas</t>
-  </si>
-  <si>
-    <t>spen</t>
-  </si>
-  <si>
-    <t>gl</t>
-  </si>
-  <si>
-    <t>hpo</t>
-  </si>
-  <si>
-    <t>Eip63E</t>
-  </si>
-  <si>
-    <t>abd-A</t>
-  </si>
-  <si>
-    <t>dnc</t>
-  </si>
-  <si>
-    <t>eff</t>
-  </si>
-  <si>
-    <t>SelG</t>
-  </si>
-  <si>
-    <t>cnc</t>
-  </si>
-  <si>
-    <t>numb</t>
-  </si>
-  <si>
-    <t>how</t>
-  </si>
-  <si>
-    <t>Dad</t>
-  </si>
-  <si>
-    <t>foxo</t>
-  </si>
-  <si>
-    <t>thr</t>
-  </si>
-  <si>
-    <t>Lac</t>
-  </si>
-  <si>
-    <t>Sry-delta</t>
-  </si>
-  <si>
-    <t>Tm1</t>
-  </si>
-  <si>
-    <t>chic</t>
-  </si>
-  <si>
-    <t>Sb</t>
-  </si>
-  <si>
-    <t>siz</t>
-  </si>
-  <si>
-    <t>disco</t>
-  </si>
-  <si>
-    <t>frc</t>
-  </si>
-  <si>
-    <t>th</t>
-  </si>
-  <si>
-    <t>oaf</t>
-  </si>
-  <si>
-    <t>pnr</t>
-  </si>
-  <si>
-    <t>ofs</t>
-  </si>
-  <si>
-    <t>RpL30</t>
-  </si>
-  <si>
-    <t>E(z)</t>
-  </si>
-  <si>
-    <t>Dl</t>
-  </si>
-  <si>
-    <t>trc</t>
-  </si>
-  <si>
-    <t>Pgant35A</t>
+    <t>CG17470</t>
+  </si>
+  <si>
+    <t>CG14995</t>
+  </si>
+  <si>
+    <t>dec-1</t>
+  </si>
+  <si>
+    <t>Sema-1b</t>
+  </si>
+  <si>
+    <t>Hs6st</t>
   </si>
   <si>
     <t>rdo</t>
-  </si>
-  <si>
-    <t>18w</t>
-  </si>
-  <si>
-    <t>Vhl</t>
-  </si>
-  <si>
-    <t>fal</t>
-  </si>
-  <si>
-    <t>elav</t>
-  </si>
-  <si>
-    <t>Pka-C3</t>
-  </si>
-  <si>
-    <t>ALiX</t>
-  </si>
-  <si>
-    <t>B4</t>
-  </si>
-  <si>
-    <t>scra</t>
-  </si>
-  <si>
-    <t>sn</t>
-  </si>
-  <si>
-    <t>xmas-2</t>
-  </si>
-  <si>
-    <t>grp</t>
-  </si>
-  <si>
-    <t>dos</t>
-  </si>
-  <si>
-    <t>Dcp-1</t>
-  </si>
-  <si>
-    <t>cactin</t>
-  </si>
-  <si>
-    <t>hep</t>
-  </si>
-  <si>
-    <t>inaC</t>
-  </si>
-  <si>
-    <t>Oseg1</t>
-  </si>
-  <si>
-    <t>yrt</t>
-  </si>
-  <si>
-    <t>Hs6st</t>
-  </si>
-  <si>
-    <t>Abl</t>
-  </si>
-  <si>
-    <t>Sh</t>
-  </si>
-  <si>
-    <t>Fas3</t>
   </si>
 </sst>
 </file>
@@ -837,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B104"/>
+  <dimension ref="A1:B92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -861,79 +705,79 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -941,628 +785,628 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B29" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B34" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="B38" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="B41" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="B43" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B45" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="B46" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="B51" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="B52" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>91</v>
+        <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="B54" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="B55" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="B56" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="B57" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="B58" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="B59" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="B60" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="B61" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="B62" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="B63" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="B64" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="B65" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="B66" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="B67" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="B68" t="s">
-        <v>118</v>
+        <v>79</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B69" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="B70" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="B71" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="B72" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B73" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B74" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B75" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B76" t="s">
-        <v>126</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>127</v>
+        <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>128</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="B78" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>134</v>
+        <v>92</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>136</v>
+        <v>92</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>138</v>
+        <v>92</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="B86" t="s">
-        <v>141</v>
+        <v>102</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="B87" t="s">
-        <v>142</v>
+        <v>104</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="B88" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>143</v>
+        <v>75</v>
       </c>
       <c r="B89" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="B90" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="B91" t="s">
         <v>110</v>
@@ -1570,106 +1414,10 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="B92" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="A93" t="s">
-        <v>147</v>
-      </c>
-      <c r="B93" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="A94" t="s">
-        <v>148</v>
-      </c>
-      <c r="B94" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95" t="s">
-        <v>149</v>
-      </c>
-      <c r="B95" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="A96" t="s">
-        <v>151</v>
-      </c>
-      <c r="B96" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97" t="s">
-        <v>152</v>
-      </c>
-      <c r="B97" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98" t="s">
-        <v>154</v>
-      </c>
-      <c r="B98" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99" t="s">
-        <v>155</v>
-      </c>
-      <c r="B99" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" t="s">
-        <v>156</v>
-      </c>
-      <c r="B100" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" t="s">
-        <v>106</v>
-      </c>
-      <c r="B101" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102" t="s">
-        <v>159</v>
-      </c>
-      <c r="B102" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103" t="s">
-        <v>161</v>
-      </c>
-      <c r="B103" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104" t="s">
-        <v>163</v>
-      </c>
-      <c r="B104" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
